--- a/tables/Parameters/Luminosity.xlsx
+++ b/tables/Parameters/Luminosity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,75 +466,85 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>V_err</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>BCv</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>(B-V)0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Rv</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rv_err</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Mbol</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Mv</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>L+</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>L-</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>d+</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>d-</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Teff</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Teff_err</t>
         </is>
@@ -571,65 +581,71 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>-3.42</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>-0.27</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>3.16</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.15</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>-8.50532122776198</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>-5.08532122776198</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>O6.5III</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>198668.261371504</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>44869.4476927578</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>33701.3277793123</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>6752.4946</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>678.6587</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>455.1382000000003</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>34500</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -664,65 +680,69 @@
       <c r="H3" t="n">
         <v>0.02</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.7040000000000006</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>-0.26</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>3.16</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.15</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>-9.20573104230982</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>-8.82173104230982</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>-6.50173104230982</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>B0.2Ia</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>378697.481532523</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>65928.0469495372</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>75599.1428067363</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
+          <t>265884.130512809</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>46288.1912196714</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>53078.2836773541</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
         <v>5535.3643</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>352.5882999999994</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>444.3267000000005</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>24000</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -757,65 +777,71 @@
       <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>-3.32</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>-0.27</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>3.16</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.15</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>-9.34461962281793</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>-6.02461962281793</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>O6.5Iaf+</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>430375.806074179</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>59772.8357455441</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>49829.8400709757</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>1513.9932</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>78.38200000000006</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>52.65149999999994</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>35895</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -850,65 +876,71 @@
       <c r="H5" t="n">
         <v>0.01</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>-3.16</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>-0.27</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>3.4</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>-7.72873449531503</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>-4.56873449531503</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>O8III</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>97161.4076496157</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>18580.6987382659</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>18580.6987382659</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>48590</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>4000</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>4000</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>32573</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -943,65 +975,69 @@
       <c r="H6" t="n">
         <v>0.01</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-2.74</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>-0.26</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>2.53</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>-8.84561447195190</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>-8.45561447195190</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>-6.10561447195190</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>B0Ib</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>271797.707162782</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>43425.0412462522</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>43425.0412462522</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
+          <t>189777.966494933</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>30320.7709465210</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>30320.7709465210</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
         <v>62440</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>4000</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>4000</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>24380</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1036,65 +1072,69 @@
       <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.6500000000000004</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>-0.26</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>3.16</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.15</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>-9.68375611051318</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-9.19375611051318</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>-7.03375611051318</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>B0.5Iae</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>588169.424345731</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>64991.2299955974</t>
-        </is>
-      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>67721.9679443754</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
+          <t>374543.654958348</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>41386.1241594926</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>43125.0458540477</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
         <v>1969.4784</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>60.11470000000008</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>68.04140000000007</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>22370</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>1000</v>
       </c>
     </row>

--- a/tables/Parameters/Luminosity.xlsx
+++ b/tables/Parameters/Luminosity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Teff_err</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Teff_model</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -648,6 +653,9 @@
       <c r="Y2" t="n">
         <v>1000</v>
       </c>
+      <c r="Z2" t="n">
+        <v>27000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -745,6 +753,9 @@
       <c r="Y3" t="n">
         <v>1000</v>
       </c>
+      <c r="Z3" t="n">
+        <v>28000</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -844,6 +855,9 @@
       <c r="Y4" t="n">
         <v>1000</v>
       </c>
+      <c r="Z4" t="n">
+        <v>30000</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -943,6 +957,9 @@
       <c r="Y5" t="n">
         <v>1000</v>
       </c>
+      <c r="Z5" t="n">
+        <v>31000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1040,6 +1057,9 @@
       <c r="Y6" t="n">
         <v>1000</v>
       </c>
+      <c r="Z6" t="n">
+        <v>23000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1136,6 +1156,9 @@
       </c>
       <c r="Y7" t="n">
         <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20000</v>
       </c>
     </row>
   </sheetData>
